--- a/erp-server/erp-server-wms/src/main/resources/excel/otherInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherInstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27360" windowHeight="8235"/>
+    <workbookView windowWidth="27450" windowHeight="8235"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <r>
       <rPr>
@@ -173,36 +173,6 @@
   </si>
   <si>
     <t>入库备注</t>
-  </si>
-  <si>
-    <t>{.type}</t>
-  </si>
-  <si>
-    <t>{.billDate}</t>
-  </si>
-  <si>
-    <t>{.warehouseName}</t>
-  </si>
-  <si>
-    <t>{.inventoryDirection}</t>
-  </si>
-  <si>
-    <t>{.receiverName}</t>
-  </si>
-  <si>
-    <t>{.deptName}</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.actualQty}</t>
-  </si>
-  <si>
-    <t>{.warehouseLocation}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
   </si>
 </sst>
 </file>
@@ -1148,8 +1118,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="2" max="2" width="23.25" customWidth="1"/>
@@ -1195,44 +1165,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D3:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D2:D1048576">
       <formula1>"普通,退货"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
       <formula1>"样品领用,KOL寄送,辅料包材,配件,报废,报损"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherInstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27450" windowHeight="8235"/>
+    <workbookView windowWidth="24960" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1171,7 +1171,7 @@
       <formula1>"普通,退货"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
-      <formula1>"样品领用,KOL寄送,辅料包材,配件,报废,报损"</formula1>
+      <formula1>"样品归还,三无产品,报溢"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherInstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherInstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24960" windowHeight="9795"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1171,7 +1171,7 @@
       <formula1>"普通,退货"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
-      <formula1>"样品归还,三无产品,报溢"</formula1>
+      <formula1>"样品归还,三无产品,库存差异调整,赠品入库"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
